--- a/cuadros/MAYO/VILLAS DE ARAGUA.xlsx
+++ b/cuadros/MAYO/VILLAS DE ARAGUA.xlsx
@@ -64,7 +64,7 @@
     <t>AGROPECUARIA LATIN FRUITS C.A.</t>
   </si>
   <si>
-    <t xml:space="preserve"> 006512</t>
+    <t>6512</t>
   </si>
   <si>
     <t>2026-05-03</t>
@@ -97,7 +97,7 @@
     <t>NRO DE CONTROL CORRECTO: 00000302</t>
   </si>
   <si>
-    <t>ERROR DE TARA EN LIMON, TARA CORRECTA: 2,4KG</t>
+    <t xml:space="preserve">LA SPCP SUJEIN AGREGO UNA TARA ERRONEA EN EL PESAJE DE LIMON, TARA CORRECTA: 2,4KG </t>
   </si>
   <si>
     <t>SIN FOTO</t>

--- a/cuadros/MAYO/VILLAS DE ARAGUA.xlsx
+++ b/cuadros/MAYO/VILLAS DE ARAGUA.xlsx
@@ -1,136 +1,42 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
-  <workbookPr defaultThemeVersion="124226"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <workbookPr/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
+  <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="32">
-  <si>
-    <t>SUCURSAL</t>
-  </si>
-  <si>
-    <t>PROVEEDOR</t>
-  </si>
-  <si>
-    <t>FACTURA</t>
-  </si>
-  <si>
-    <t>FECHA</t>
-  </si>
-  <si>
-    <t>TIPO FISCALIZACIÓN</t>
-  </si>
-  <si>
-    <t>RESPONSABLE</t>
-  </si>
-  <si>
-    <t>INCIDENCIA</t>
-  </si>
-  <si>
-    <t>TIPO DE ERROR</t>
-  </si>
-  <si>
-    <t>OBSERVACIÓN</t>
-  </si>
-  <si>
-    <t>MONTO $</t>
-  </si>
-  <si>
-    <t>F COBRADA</t>
-  </si>
-  <si>
-    <t>CLASIFICACIÓN MONTO</t>
-  </si>
-  <si>
-    <t>ID</t>
-  </si>
-  <si>
-    <t>VILLAS DE ARAGUA</t>
-  </si>
-  <si>
-    <t>GRUPO LP2024, C.A.</t>
-  </si>
-  <si>
-    <t>AGROPECUARIA LATIN FRUITS C.A.</t>
-  </si>
-  <si>
-    <t>6512</t>
-  </si>
-  <si>
-    <t>2026-05-03</t>
-  </si>
-  <si>
-    <t>2026-05-04</t>
-  </si>
-  <si>
-    <t>RECEPCION</t>
-  </si>
-  <si>
-    <t>GTE FANNY VEGAS</t>
-  </si>
-  <si>
-    <t>SPCP SUJEIN MACHADO</t>
-  </si>
-  <si>
-    <t>NÚMERO DE CONTROL O DOCUMENTO ERRÓNEO.</t>
-  </si>
-  <si>
-    <t>ERROR DE KG EN TARA.</t>
-  </si>
-  <si>
-    <t>TIPO A</t>
-  </si>
-  <si>
-    <t>TIPO C</t>
-  </si>
-  <si>
-    <t>NRO DE CONTROL CORRECTO: 00000302</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LA SPCP SUJEIN AGREGO UNA TARA ERRONEA EN EL PESAJE DE LIMON, TARA CORRECTA: 2,4KG </t>
-  </si>
-  <si>
-    <t>SIN FOTO</t>
-  </si>
-  <si>
-    <t>NINGUNA</t>
-  </si>
-  <si>
-    <t>20260504132300</t>
-  </si>
-  <si>
-    <t>20260504132941</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
   <fonts count="1">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF92D050"/>
+        <bgColor rgb="FF92D050"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -145,14 +51,82 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+  <cellXfs count="2">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -440,131 +414,271 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M3"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:N4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:13">
-      <c r="A1" t="s">
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>SUCURSAL</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>PROVEEDOR</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>FACTURA</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>FECHA</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>TIPO FISCALIZACIÓN</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>RESPONSABLE</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>INCIDENCIA</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>TIPO DE ERROR</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>OBSERVACIÓN</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>MONTO $</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>F COBRADA</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>CLASIFICACIÓN MONTO</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>FOTO_INCIDENCIA</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>VILLAS DE ARAGUA</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>GRUPO LP2024, C.A.</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>2</v>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>2026-05-03</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>RECEPCION</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>GTE FANNY VEGAS</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>NÚMERO DE CONTROL O DOCUMENTO ERRÓNEO.</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>TIPO A</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>NRO DE CONTROL CORRECTO: 00000302</t>
+        </is>
+      </c>
+      <c r="J2" t="n">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" t="s">
-        <v>8</v>
-      </c>
-      <c r="J1" t="s">
-        <v>9</v>
-      </c>
-      <c r="K1" t="s">
-        <v>10</v>
-      </c>
-      <c r="L1" t="s">
-        <v>11</v>
-      </c>
-      <c r="M1" t="s">
-        <v>12</v>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>SIN FOTO</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>NINGUNA</t>
+        </is>
+      </c>
+      <c r="M2" t="n">
+        <v>20260504132300</v>
       </c>
     </row>
-    <row r="2" spans="1:13">
-      <c r="A2" t="s">
-        <v>13</v>
-      </c>
-      <c r="B2" t="s">
-        <v>14</v>
-      </c>
-      <c r="C2">
-        <v>2</v>
-      </c>
-      <c r="D2" t="s">
-        <v>17</v>
-      </c>
-      <c r="E2" t="s">
-        <v>19</v>
-      </c>
-      <c r="F2" t="s">
-        <v>20</v>
-      </c>
-      <c r="G2" t="s">
-        <v>22</v>
-      </c>
-      <c r="H2" t="s">
-        <v>24</v>
-      </c>
-      <c r="I2" t="s">
-        <v>26</v>
-      </c>
-      <c r="J2">
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>VILLAS DE ARAGUA</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>AGROPECUARIA LATIN FRUITS C.A.</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>6512</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>RECEPCION</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>SPCP SUJEIN MACHADO</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>ERROR DE KG EN TARA.</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>TIPO C</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LA SPCP SUJEIN AGREGO UNA TARA ERRONEA EN EL PESAJE DE LIMON, TARA CORRECTA: 2,4KG </t>
+        </is>
+      </c>
+      <c r="J3" t="n">
         <v>0</v>
       </c>
-      <c r="K2" t="s">
-        <v>28</v>
-      </c>
-      <c r="L2" t="s">
-        <v>29</v>
-      </c>
-      <c r="M2" t="s">
-        <v>30</v>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>SIN FOTO</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>NINGUNA</t>
+        </is>
+      </c>
+      <c r="M3" t="n">
+        <v>20260504132941</v>
       </c>
     </row>
-    <row r="3" spans="1:13">
-      <c r="A3" t="s">
-        <v>13</v>
-      </c>
-      <c r="B3" t="s">
-        <v>15</v>
-      </c>
-      <c r="C3" t="s">
-        <v>16</v>
-      </c>
-      <c r="D3" t="s">
-        <v>18</v>
-      </c>
-      <c r="E3" t="s">
-        <v>19</v>
-      </c>
-      <c r="F3" t="s">
-        <v>21</v>
-      </c>
-      <c r="G3" t="s">
-        <v>23</v>
-      </c>
-      <c r="H3" t="s">
-        <v>25</v>
-      </c>
-      <c r="I3" t="s">
-        <v>27</v>
-      </c>
-      <c r="J3">
-        <v>0</v>
-      </c>
-      <c r="K3" t="s">
-        <v>28</v>
-      </c>
-      <c r="L3" t="s">
-        <v>29</v>
-      </c>
-      <c r="M3" t="s">
-        <v>31</v>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>VILLAS DE ARAGUA</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>DISTRIBUIDORA JORIAN,C.A</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>002287</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>RECEPCION</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SUB GERENTE JORGE GONZALES </t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>DIFERENCIA ENTRE CANTIDAD FISCALIZADA Y DOCUMENTO.</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>TIPO D</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">EL SUG GERENTE JORGE CONTABILIZO MAL LA CANTIDAD DE PIÑAS RECIBIDAS, SE CONSTATO QUE SOLO INGRESARON 44UND DE LAS 46UND QUE INDICA LA FACTURA. </t>
+        </is>
+      </c>
+      <c r="J4" s="1" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>SIN_FOTO</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>COBRO</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>ID_20260505140415</t>
+        </is>
       </c>
     </row>
   </sheetData>

--- a/cuadros/MAYO/VILLAS DE ARAGUA.xlsx
+++ b/cuadros/MAYO/VILLAS DE ARAGUA.xlsx
@@ -2,8 +2,9 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
+  <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
@@ -25,18 +26,12 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="2">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF92D050"/>
-        <bgColor rgb="FF92D050"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -51,12 +46,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
@@ -419,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N4"/>
+  <dimension ref="A1:N5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -554,6 +548,7 @@
       <c r="M2" t="n">
         <v>20260504132300</v>
       </c>
+      <c r="N2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -615,6 +610,7 @@
       <c r="M3" t="n">
         <v>20260504132941</v>
       </c>
+      <c r="N3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -627,10 +623,8 @@
           <t>DISTRIBUIDORA JORIAN,C.A</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>002287</t>
-        </is>
+      <c r="C4" t="n">
+        <v>2287</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -662,7 +656,7 @@
           <t xml:space="preserve">EL SUG GERENTE JORGE CONTABILIZO MAL LA CANTIDAD DE PIÑAS RECIBIDAS, SE CONSTATO QUE SOLO INGRESARON 44UND DE LAS 46UND QUE INDICA LA FACTURA. </t>
         </is>
       </c>
-      <c r="J4" s="1" t="n">
+      <c r="J4" t="n">
         <v>3.14</v>
       </c>
       <c r="K4" t="inlineStr">
@@ -678,10 +672,81 @@
       <c r="M4" t="inlineStr">
         <is>
           <t>ID_20260505140415</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>VILLAS DE ARAGUA</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>PROCESADORA DE VEGETALES Y FRUTAS PROVEFRU, C.A.</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>21823</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>RECEPCION</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>SUB GERENTE JOSE QUINTERO</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>NO SE INDICÓ DIFERENCIA AL DORSO DE LA FACTURA.</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>TIPO D</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">EL SUB. GERENTE JOSE NO COLOCO NOTA AL DORSO DE LAS 3 UNIDADES DE VAINITAS, POR LO QUE CANCELA EL FALTANTE </t>
+        </is>
+      </c>
+      <c r="J5" t="n">
+        <v>7.86</v>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>00024037.jpeg</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>COBRO</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>ID_20260507162836</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>INC_162836.jpeg</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/cuadros/MAYO/VILLAS DE ARAGUA.xlsx
+++ b/cuadros/MAYO/VILLAS DE ARAGUA.xlsx
@@ -26,12 +26,18 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF92D050"/>
+        <bgColor rgb="FF92D050"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -46,8 +52,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -548,7 +555,6 @@
       <c r="M2" t="n">
         <v>20260504132300</v>
       </c>
-      <c r="N2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -610,7 +616,6 @@
       <c r="M3" t="n">
         <v>20260504132941</v>
       </c>
-      <c r="N3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -656,7 +661,7 @@
           <t xml:space="preserve">EL SUG GERENTE JORGE CONTABILIZO MAL LA CANTIDAD DE PIÑAS RECIBIDAS, SE CONSTATO QUE SOLO INGRESARON 44UND DE LAS 46UND QUE INDICA LA FACTURA. </t>
         </is>
       </c>
-      <c r="J4" t="n">
+      <c r="J4" s="1" t="n">
         <v>3.14</v>
       </c>
       <c r="K4" t="inlineStr">
@@ -674,7 +679,6 @@
           <t>ID_20260505140415</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -722,7 +726,7 @@
           <t xml:space="preserve">EL SUB. GERENTE JOSE NO COLOCO NOTA AL DORSO DE LAS 3 UNIDADES DE VAINITAS, POR LO QUE CANCELA EL FALTANTE </t>
         </is>
       </c>
-      <c r="J5" t="n">
+      <c r="J5" s="1" t="n">
         <v>7.86</v>
       </c>
       <c r="K5" t="inlineStr">

--- a/cuadros/MAYO/VILLAS DE ARAGUA.xlsx
+++ b/cuadros/MAYO/VILLAS DE ARAGUA.xlsx
@@ -808,7 +808,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>SIN_FOTO</t>
+          <t>COB_075125_0.jpeg</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
